--- a/cet4/result/73_重生商女_绝地反击的逆袭/73_重生商女_绝地反击的逆袭_学习版.xlsx
+++ b/cet4/result/73_重生商女_绝地反击的逆袭/73_重生商女_绝地反击的逆袭_学习版.xlsx
@@ -397,857 +397,717 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D50"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>floor</v>
       </c>
       <c r="B2" t="str">
-        <v>floor</v>
+        <v>/flɔːr/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D2" t="str">
         <v>地板</v>
       </c>
-      <c r="D2" t="str">
-        <v>floor(地板)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>sadness</v>
       </c>
       <c r="B3" t="str">
-        <v>sadness</v>
+        <v>/ˈsædnəs/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>悲哀</v>
       </c>
-      <c r="D3" t="str">
-        <v>sadness(悲哀)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>rejection</v>
       </c>
       <c r="B4" t="str">
-        <v>rejection</v>
+        <v/>
       </c>
       <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
         <v>拒绝</v>
       </c>
-      <c r="D4" t="str">
-        <v>rejection(拒绝)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>classmate</v>
       </c>
       <c r="B5" t="str">
-        <v>classmate</v>
+        <v>/ˈklæsmeɪt/</v>
       </c>
       <c r="C5" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>同班同学</v>
       </c>
-      <c r="D5" t="str">
-        <v>classmate(同班同学)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>elaborate</v>
       </c>
       <c r="B6" t="str">
-        <v>elaborate</v>
+        <v>/ɪˈlæbərət; ɪˈlæbəreɪt; ɪˈlæbərɪt/</v>
       </c>
       <c r="C6" t="str">
+        <v>vt./vi./adj.</v>
+      </c>
+      <c r="D6" t="str">
         <v>精心制作的</v>
       </c>
-      <c r="D6" t="str">
-        <v>elaborate(精心制作的)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>ordinary</v>
       </c>
       <c r="B7" t="str">
-        <v>ordinary</v>
+        <v>/ˈɔːrdneri/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D7" t="str">
         <v>普通的</v>
       </c>
-      <c r="D7" t="str">
-        <v>ordinary(普通的)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>brook</v>
       </c>
       <c r="B8" t="str">
-        <v>brook</v>
+        <v>/brʊk/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D8" t="str">
         <v>小溪</v>
       </c>
-      <c r="D8" t="str">
-        <v>brook(小溪)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>she</v>
       </c>
       <c r="B9" t="str">
-        <v>she</v>
+        <v>/ʃi,ʃiː/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./pron.</v>
+      </c>
+      <c r="D9" t="str">
         <v>她</v>
       </c>
-      <c r="D9" t="str">
-        <v>she(她)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>vinegar</v>
       </c>
       <c r="B10" t="str">
-        <v>vinegar</v>
+        <v>/ˈvɪnɪɡər/</v>
       </c>
       <c r="C10" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>醋</v>
       </c>
-      <c r="D10" t="str">
-        <v>vinegar(醋)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>old</v>
       </c>
       <c r="B11" t="str">
-        <v>old</v>
+        <v>/oʊld/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D11" t="str">
         <v>古老的</v>
       </c>
-      <c r="D11" t="str">
-        <v>old(古老的)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>portrait</v>
       </c>
       <c r="B12" t="str">
-        <v>portrait</v>
+        <v>/ˈpɔːrtrət/</v>
       </c>
       <c r="C12" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>肖像</v>
       </c>
-      <c r="D12" t="str">
-        <v>portrait(肖像)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>vibration</v>
       </c>
       <c r="B13" t="str">
-        <v>vibration</v>
+        <v>/vaɪˈbreɪʃn/</v>
       </c>
       <c r="C13" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>振动</v>
       </c>
-      <c r="D13" t="str">
-        <v>vibration(振动)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>construction</v>
       </c>
       <c r="B14" t="str">
-        <v>construction</v>
+        <v>/kənˈstrʌkʃn/</v>
       </c>
       <c r="C14" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>建设</v>
       </c>
-      <c r="D14" t="str">
-        <v>construction(建设)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>draft</v>
       </c>
       <c r="B15" t="str">
-        <v>draft</v>
+        <v>/dræft/</v>
       </c>
       <c r="C15" t="str">
+        <v>n./vt./v.</v>
+      </c>
+      <c r="D15" t="str">
         <v>草稿</v>
       </c>
-      <c r="D15" t="str">
-        <v>draft(草稿)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>trust</v>
       </c>
       <c r="B16" t="str">
-        <v>trust</v>
+        <v>/trʌst/</v>
       </c>
       <c r="C16" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D16" t="str">
         <v>信任</v>
       </c>
-      <c r="D16" t="str">
-        <v>trust(信任)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>rumour</v>
       </c>
       <c r="B17" t="str">
-        <v>rumour</v>
+        <v>/ˈruːmər/</v>
       </c>
       <c r="C17" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D17" t="str">
         <v>谣言</v>
       </c>
-      <c r="D17" t="str">
-        <v>rumour(谣言)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>council</v>
       </c>
       <c r="B18" t="str">
-        <v>council</v>
+        <v>/ˈkaʊnsl/</v>
       </c>
       <c r="C18" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>委员会</v>
       </c>
-      <c r="D18" t="str">
-        <v>council(委员会)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>make</v>
       </c>
       <c r="B19" t="str">
-        <v>make</v>
+        <v>/meɪk/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D19" t="str">
         <v>制造</v>
       </c>
-      <c r="D19" t="str">
-        <v>make(制造)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>neat</v>
       </c>
       <c r="B20" t="str">
-        <v>neat</v>
+        <v>/niːt/</v>
       </c>
       <c r="C20" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D20" t="str">
         <v>整洁的</v>
       </c>
-      <c r="D20" t="str">
-        <v>neat(整洁的)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>linen</v>
       </c>
       <c r="B21" t="str">
-        <v>linen</v>
+        <v>/ˈlɪnɪn/</v>
       </c>
       <c r="C21" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D21" t="str">
         <v>亚麻布</v>
       </c>
-      <c r="D21" t="str">
-        <v>linen(亚麻布)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>bulk</v>
       </c>
       <c r="B22" t="str">
-        <v>bulk</v>
+        <v>/bʌlk/</v>
       </c>
       <c r="C22" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D22" t="str">
         <v>大部分</v>
       </c>
-      <c r="D22" t="str">
-        <v>bulk(大部分)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>load</v>
       </c>
       <c r="B23" t="str">
-        <v>load</v>
+        <v>/loʊd/</v>
       </c>
       <c r="C23" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D23" t="str">
         <v>负载</v>
       </c>
-      <c r="D23" t="str">
-        <v>load(负载)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>compute</v>
       </c>
       <c r="B24" t="str">
-        <v>compute</v>
+        <v>/kəmˈpjuːt/</v>
       </c>
       <c r="C24" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D24" t="str">
         <v>计算</v>
       </c>
-      <c r="D24" t="str">
-        <v>compute(计算)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>coal</v>
       </c>
       <c r="B25" t="str">
-        <v>coal</v>
+        <v>/koʊl/</v>
       </c>
       <c r="C25" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D25" t="str">
         <v>煤</v>
       </c>
-      <c r="D25" t="str">
-        <v>coal(煤)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>excess</v>
       </c>
       <c r="B26" t="str">
-        <v>excess</v>
+        <v>/ɪkˈses/</v>
       </c>
       <c r="C26" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D26" t="str">
         <v>超过</v>
       </c>
-      <c r="D26" t="str">
-        <v>excess(超过)📢</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>heat</v>
       </c>
       <c r="B27" t="str">
-        <v>heat</v>
+        <v>/hiːt/</v>
       </c>
       <c r="C27" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D27" t="str">
         <v>高温</v>
       </c>
-      <c r="D27" t="str">
-        <v>heat(高温)📢</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>splash</v>
       </c>
       <c r="B28" t="str">
-        <v>splash</v>
+        <v>/splæʃ/</v>
       </c>
       <c r="C28" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D28" t="str">
         <v>溅</v>
       </c>
-      <c r="D28" t="str">
-        <v>splash(溅)📢</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>political</v>
       </c>
       <c r="B29" t="str">
-        <v>political</v>
+        <v>/pəˈlɪtɪkl/</v>
       </c>
       <c r="C29" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D29" t="str">
         <v>政治的</v>
       </c>
-      <c r="D29" t="str">
-        <v>political(政治的)📢</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>radioactivity</v>
       </c>
       <c r="B30" t="str">
-        <v>radioactivity</v>
+        <v>/ˌreɪdioʊækˈtɪvəti/</v>
       </c>
       <c r="C30" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D30" t="str">
         <v>放射性</v>
       </c>
-      <c r="D30" t="str">
-        <v>radioactivity(放射性)📢</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>across</v>
       </c>
       <c r="B31" t="str">
-        <v>across</v>
+        <v>/əˈkrɔːs/</v>
       </c>
       <c r="C31" t="str">
+        <v>v./adv./prep.</v>
+      </c>
+      <c r="D31" t="str">
         <v>横过</v>
       </c>
-      <c r="D31" t="str">
-        <v>across(横过)📢</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>hostile</v>
       </c>
       <c r="B32" t="str">
-        <v>hostile</v>
+        <v>/ˈhɑːstl,ˈhɑːstaɪl/</v>
       </c>
       <c r="C32" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D32" t="str">
         <v>敌对的</v>
       </c>
-      <c r="D32" t="str">
-        <v>hostile(敌对的)📢</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>bill</v>
       </c>
       <c r="B33" t="str">
-        <v>bill</v>
+        <v>/bɪl/</v>
       </c>
       <c r="C33" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D33" t="str">
         <v>法案</v>
       </c>
-      <c r="D33" t="str">
-        <v>bill(法案)📢</v>
-      </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>disappear</v>
       </c>
       <c r="B34" t="str">
-        <v>disappear</v>
+        <v>/ˌdɪsəˈpɪr/</v>
       </c>
       <c r="C34" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D34" t="str">
         <v>消失</v>
       </c>
-      <c r="D34" t="str">
-        <v>disappear(消失)📢</v>
-      </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>harden</v>
       </c>
       <c r="B35" t="str">
-        <v>harden</v>
+        <v>/ˈhɑːrdn/</v>
       </c>
       <c r="C35" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D35" t="str">
         <v>变坚强</v>
       </c>
-      <c r="D35" t="str">
-        <v>harden(变坚强)📢</v>
-      </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>aspect</v>
       </c>
       <c r="B36" t="str">
-        <v>aspect</v>
+        <v>/ˈæspekt/</v>
       </c>
       <c r="C36" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D36" t="str">
         <v>方面</v>
       </c>
-      <c r="D36" t="str">
-        <v>aspect(方面)📢</v>
-      </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>inner</v>
       </c>
       <c r="B37" t="str">
-        <v>inner</v>
+        <v>/ˈɪnər/</v>
       </c>
       <c r="C37" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D37" t="str">
         <v>内心</v>
       </c>
-      <c r="D37" t="str">
-        <v>inner(内心)📢</v>
-      </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>resignation</v>
       </c>
       <c r="B38" t="str">
-        <v>trust</v>
+        <v>/ˌrezɪɡˈneɪʃn/</v>
       </c>
       <c r="C38" t="str">
-        <v>信任</v>
+        <v>n.</v>
       </c>
       <c r="D38" t="str">
-        <v>trust(信任)📢</v>
+        <v>辞职</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>certainty</v>
       </c>
       <c r="B39" t="str">
-        <v>resignation</v>
+        <v>/ˈsɜːrtnti/</v>
       </c>
       <c r="C39" t="str">
-        <v>辞职</v>
+        <v>n.</v>
       </c>
       <c r="D39" t="str">
-        <v>resignation(辞职)📢</v>
+        <v>确实</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>automatic</v>
       </c>
       <c r="B40" t="str">
-        <v>certainty</v>
+        <v>/ˌɔːtəˈmætɪk/</v>
       </c>
       <c r="C40" t="str">
-        <v>确实</v>
+        <v>n./adj.</v>
       </c>
       <c r="D40" t="str">
-        <v>certainty(确实)📢</v>
+        <v>自动的</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>worthy</v>
       </c>
       <c r="B41" t="str">
-        <v>automatic</v>
+        <v>/ˈwɜːrði/</v>
       </c>
       <c r="C41" t="str">
-        <v>自动的</v>
+        <v>n./adj.</v>
       </c>
       <c r="D41" t="str">
-        <v>automatic(自动的)📢</v>
+        <v>值得的</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>sale</v>
       </c>
       <c r="B42" t="str">
-        <v>worthy</v>
+        <v>/seɪl/</v>
       </c>
       <c r="C42" t="str">
-        <v>值得的</v>
+        <v>n.</v>
       </c>
       <c r="D42" t="str">
-        <v>worthy(值得的)📢</v>
+        <v>销售</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>reproach</v>
       </c>
       <c r="B43" t="str">
-        <v>trust</v>
+        <v>/rɪˈproʊtʃ/</v>
       </c>
       <c r="C43" t="str">
-        <v>信任</v>
+        <v>n./vt.</v>
       </c>
       <c r="D43" t="str">
-        <v>trust(信任)📢</v>
+        <v>责备</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>stupid</v>
       </c>
       <c r="B44" t="str">
-        <v>sale</v>
+        <v>/ˈstuːpɪd/</v>
       </c>
       <c r="C44" t="str">
-        <v>销售</v>
+        <v>n./adj.</v>
       </c>
       <c r="D44" t="str">
-        <v>sale(销售)📢</v>
+        <v>愚蠢的</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>outside</v>
       </c>
       <c r="B45" t="str">
-        <v>reproach</v>
+        <v>/ˌaʊtˈsaɪd/</v>
       </c>
       <c r="C45" t="str">
-        <v>责备</v>
+        <v>n./v./adj./adv./prep.</v>
       </c>
       <c r="D45" t="str">
-        <v>reproach(责备)📢</v>
+        <v>外面</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>canteen</v>
       </c>
       <c r="B46" t="str">
-        <v>stupid</v>
+        <v>/kænˈtiːn/</v>
       </c>
       <c r="C46" t="str">
-        <v>愚蠢的</v>
+        <v>n.</v>
       </c>
       <c r="D46" t="str">
-        <v>stupid(愚蠢的)📢</v>
+        <v>食堂</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>post</v>
       </c>
       <c r="B47" t="str">
-        <v>outside</v>
+        <v>/poʊst/</v>
       </c>
       <c r="C47" t="str">
-        <v>外面</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D47" t="str">
-        <v>outside(外面)📢</v>
+        <v>岗位</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>death</v>
       </c>
       <c r="B48" t="str">
-        <v>trust</v>
+        <v>/deθ/</v>
       </c>
       <c r="C48" t="str">
-        <v>信任</v>
+        <v>n.</v>
       </c>
       <c r="D48" t="str">
-        <v>trust(信任)📢</v>
+        <v>死亡</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>outdoor</v>
       </c>
       <c r="B49" t="str">
-        <v>worthy</v>
+        <v>/ˈaʊtdɔːr/</v>
       </c>
       <c r="C49" t="str">
-        <v>值得的</v>
+        <v>adj.</v>
       </c>
       <c r="D49" t="str">
-        <v>worthy(值得的)📢</v>
+        <v>户外的</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>fan</v>
       </c>
       <c r="B50" t="str">
-        <v>canteen</v>
+        <v>/fæn/</v>
       </c>
       <c r="C50" t="str">
-        <v>食堂</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D50" t="str">
-        <v>canteen(食堂)📢</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>post</v>
-      </c>
-      <c r="C51" t="str">
-        <v>岗位</v>
-      </c>
-      <c r="D51" t="str">
-        <v>post(岗位)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>ordinary</v>
-      </c>
-      <c r="C52" t="str">
-        <v>普通的</v>
-      </c>
-      <c r="D52" t="str">
-        <v>ordinary(普通的)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>brook</v>
-      </c>
-      <c r="C53" t="str">
-        <v>小溪</v>
-      </c>
-      <c r="D53" t="str">
-        <v>brook(小溪)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>splash</v>
-      </c>
-      <c r="C54" t="str">
-        <v>溅</v>
-      </c>
-      <c r="D54" t="str">
-        <v>splash(溅)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>death</v>
-      </c>
-      <c r="C55" t="str">
-        <v>死亡</v>
-      </c>
-      <c r="D55" t="str">
-        <v>death(死亡)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>outdoor</v>
-      </c>
-      <c r="C56" t="str">
-        <v>户外的</v>
-      </c>
-      <c r="D56" t="str">
-        <v>outdoor(户外的)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>fan</v>
-      </c>
-      <c r="C57" t="str">
         <v>扇子</v>
-      </c>
-      <c r="D57" t="str">
-        <v>fan(扇子)📢</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>stupid</v>
-      </c>
-      <c r="C58" t="str">
-        <v>愚蠢的</v>
-      </c>
-      <c r="D58" t="str">
-        <v>stupid(愚蠢的)📢</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="str">
-        <v>compute</v>
-      </c>
-      <c r="C59" t="str">
-        <v>计算</v>
-      </c>
-      <c r="D59" t="str">
-        <v>compute(计算)📢</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="str">
-        <v>trust</v>
-      </c>
-      <c r="C60" t="str">
-        <v>信任</v>
-      </c>
-      <c r="D60" t="str">
-        <v>trust(信任)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D60"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D50"/>
   </ignoredErrors>
 </worksheet>
 </file>